--- a/www/download/COUNTRY.NOR.WIOD16.xlsx
+++ b/www/download/COUNTRY.NOR.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>Noruega</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>8.78076126254857</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>8.98798496076842</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>7.93210388256787</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>7.11102225356316</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>6.73424523280679</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>6.43998439742794</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>6.40702430779204</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>5.84593774822521</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>5.5627108511722</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>6.25434354345176</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>6.03727045673454</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>5.60001536334162</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>5.81412112880623</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>5.86964759545451</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>6.28032036825306</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2.328</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2.343</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2.318</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2.331</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2.362</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2.442</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2.542</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2.626</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2.612</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2.601</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2.638</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2.689</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2.727</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2.747</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.155</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2.159</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2.171</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2.144</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2.156</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2.193</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2.27</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2.374</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2.464</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.443</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2.442</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2.476</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2.526</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2.562</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2.588</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>3293.21</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3249.445</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>3223.564</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>3165.899</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>3229.615</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>3280.768</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>3384.942</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>3549.279</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>3672.623</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>3618.799</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>3612.94</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>3685.378</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>3751.593</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>3785.21</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>3830.627</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4977008532.53529</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>4776011769.93664</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>4780696134.17952</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>4877590703.22698</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4949886187.5391</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>5109390909.23057</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>5145403756.01119</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>5504694617.99188</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>5613892052.07377</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>5106745892.85579</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>5089226645.02314</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>5521067503.15223</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>5428964210.91954</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>5559029189.48371</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>5447921599.9914</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2741088835.57762</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2858978580.17506</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2999850482.22913</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3066344972.91229</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>3298193073.16132</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3304590093.66772</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3449733097.40449</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>3609879116.67003</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3688840560.97476</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3548039263.6648</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>3222577785.47051</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>3616284551.75609</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>3360507082.47205</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>3735218455.16124</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>3762762713.50427</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1226195.01055633</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1122597.62734903</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>991092.189920898</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>905879.13256831</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>801741.964453975</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>726343.357544991</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>632129.962095466</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>547679.188859236</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>492031.317821872</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>514099.858103397</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>467839.601815778</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>448284.047838479</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>435479.641079392</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>428255.070488273</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>416584.124673303</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>14720.7962548799</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>14364.9309072171</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>14446.9555662583</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>15549.0600457969</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>17481.9644255899</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>19061.8455335793</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>20770.0329726466</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>24553.7878118519</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>27464.7335173539</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>24632.2161640361</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>27232.0889875537</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>29496.9211982365</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>29293.1342005804</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>29687.251633319</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>30187.1684208163</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>40440.0167357196</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>38442.0886666181</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>38710.7489824389</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>42982.6446543517</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>48225.0810811757</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>53446.6867468365</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>56860.9097875489</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>68682.5986447112</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>76026.9215382379</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>62936.9405815446</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>69487.4950005652</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>80055.0540498697</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>76700.4109629904</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>78459.906552239</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>77247.9290248958</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.110872424300082</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.0510746812996405</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.00428370757318053</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.0457694663033944</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.0934430054047491</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.0773439629191789</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.0863061254299633</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-0.0794705604808905</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-0.0631202561146296</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-0.0448245500813679</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.0547456807171329</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-0.0412811961059865</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.050734283054249</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-0.0463743840529302</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>-0.0395355021910827</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>38828.820366918</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>39260.7429726079</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>44177.8428514702</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>49462.2851379609</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>55434.0482412998</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>62065.3812219946</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>68243.6297937369</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>82319.1801557791</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>94994.4651759168</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>92866.7440816386</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>100016.097560435</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>113571.051891685</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>114704.425789506</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>120694.928080659</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>119371.069537673</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.78076126254857</t>
+          <t>1271.96697706618</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8.98798496076842</t>
+          <t>1324.21425668136</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7.93210388256787</t>
+          <t>1381.78281079186</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7.11102225356316</t>
+          <t>1430.19821497775</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>6.73424523280679</t>
+          <t>1529.77415267223</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>6.43998439742794</t>
+          <t>1506.88102766426</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>6.40702430779204</t>
+          <t>1519.70621031035</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>5.84593774822521</t>
+          <t>1520.58934990313</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>5.5627108511722</t>
+          <t>1497.09438351248</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>6.25434354345176</t>
+          <t>1452.32880215506</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>6.03727045673454</t>
+          <t>1319.6469227971</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>5.60001536334162</t>
+          <t>1460.53495628275</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>5.81412112880623</t>
+          <t>1330.36701602219</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>5.86964759545451</t>
+          <t>1457.93070068745</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>6.28032036825306</t>
+          <t>1453.9268599321</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>7223688033.34091</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>7477772243.27635</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>7278768680.45752</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>7819357624.82086</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>8705720816.82853</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>10320932556.1016</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>10985020661.4021</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>9652172817.04197</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>11324390759.513</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>8181216540.97344</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>7976762358.49146</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>9534621680.61725</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>9520035801.49384</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>9194821767.06325</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>8295176434.01859</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>8141928513.40229</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>8475581703.56556</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>8425751212.5079</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>9036252605.60867</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>9937830936.17121</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>11546307991.8493</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>12138611727.0414</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>10927696924.2507</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>12598122691.4668</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>9520854265.68377</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>9458472691.68867</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>11095992259.8478</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>11232654107.9015</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>10888399329.2276</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>9839493675.90235</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>-918240480.061385</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-997809460.289213</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>-1146982532.05038</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-1216894980.7878</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>-1232110119.34268</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>-1225375435.74774</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>-1153591065.63923</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1275524107.2087</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-1273731931.95372</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>-1339637724.71033</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.201</t>
+          <t>-1481710333.1972</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>-1561370579.23058</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>-1712618306.4077</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1.479</t>
+          <t>-1693577562.16438</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>-1544317241.88375</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>1412.99303944316</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>1391.8480778138</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>1375.86365730078</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>1364.73880597015</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>1386.82745825603</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>1390.33287733698</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1388.54625550661</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>1399.74726200505</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>1402.5974025974</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>1387.22881702824</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.701</t>
+          <t>1391.89189189189</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>1400.24232633279</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>1397.8622327791</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>1390.32006245121</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.835</t>
+          <t>1396.44513137558</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>1414.60912399271</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>1394.61153874586</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>1375.82754217891</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>1365.78917259076</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>1385.50613662572</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>1388.97889818795</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>1386.13519163017</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>1396.25462510069</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>1398.56175010179</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>1385.45135194252</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>1389.05817665983</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>1397.03478356536</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>1395.16283188987</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>1388.04917414791</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>1394.47658196423</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>76169.7407171746</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>75982.8308532573</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>76837.4625463018</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>87363.1473215578</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>105255.951300737</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>130306.621332898</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>150426.384193555</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>169165.586702119</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>210208.385749881</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>147785.150910255</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>165868.432580254</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>200182.394155131</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>201658.65403179</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>199376.008242583</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>188130.64991241</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1373116217.79891</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1312733649.31789</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1246913085.77505</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1273731807.02916</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1258953130.99175</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1297801088.78916</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1309390035.38303</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1402050902.36158</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1445593075.92191</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1309101174.35358</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1333790741.95343</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1452478292.14393</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1392826923.31794</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1411920572.91604</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1348266185.25922</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>43577.9185603864</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>43433.8796681205</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>46897.5960105832</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>53288.3863007638</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>63734.7799524282</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>72892.5624622443</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>82617.8361641521</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>104246.627704892</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>117668.629917428</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>93370.7834897156</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>106056.366296212</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>122591.025920289</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>121378.240980899</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>127473.92008699</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>125767.145872063</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3293.21</t>
+          <t>3561336818.14788</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3249.445</t>
+          <t>3579747907.37057</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3223.564</t>
+          <t>3691124908.39707</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3165.899</t>
+          <t>3908730934.39756</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3229.615</t>
+          <t>4234960476.50883</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3280.768</t>
+          <t>4379276180.71837</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3384.942</t>
+          <t>4512230192.43856</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>3549.279</t>
+          <t>4705104013.65559</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3672.623</t>
+          <t>4803098921.02853</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3618.799</t>
+          <t>4193087728.23004</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>3612.94</t>
+          <t>4137839382.44873</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>3685.378</t>
+          <t>4620780697.72455</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>3751.593</t>
+          <t>4255284246.13863</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>3785.21</t>
+          <t>4610819769.64821</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>3830.627</t>
+          <t>4493709736.93919</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>32591.8221567882</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>32548.9511851368</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>29939.8665357186</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>34074.761020794</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>41521.1713483092</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>57414.0588706536</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>67808.5480294033</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>64918.9589972264</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>92539.7558324529</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>54414.3674205399</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>59812.0662840424</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>77591.3682348417</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>80280.4130508915</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>71902.0881555937</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>62363.5040403465</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4977.193</t>
+          <t>-2188220600.34897</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4777.318</t>
+          <t>-2267014258.05268</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4781.985</t>
+          <t>-2444211822.62202</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4878.519</t>
+          <t>-2634999127.36841</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>4950.69</t>
+          <t>-2976007345.51709</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>5109.623</t>
+          <t>-3081475091.92921</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>5146.068</t>
+          <t>-3202840157.05553</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>5506.037</t>
+          <t>-3303053111.29401</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>5614.162</t>
+          <t>-3357505845.10661</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>5107.29</t>
+          <t>-2883986553.87646</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>5090.553</t>
+          <t>-2804048640.49529</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>5522.959</t>
+          <t>-3168302405.58062</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>5429.506</t>
+          <t>-2862457322.82069</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>5559.204</t>
+          <t>-3198899196.73217</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>5447.408</t>
+          <t>-3145443551.67997</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>92424.951764</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>92471.19002</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>101459.41938</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>117854.285501</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>139672.516176</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>170088.58776</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>194491.293048</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>216227.57548</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>265273.75036</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>204186.24745</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>227555.42334</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>272728.5513</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>276890.684532</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>281556.238994</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>266179.601988253</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1811.709</t>
+          <t>0.0792033575048217</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1784.687</t>
+          <t>0.0743877611300407</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1784.169</t>
+          <t>0.0639537382664462</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1764.478</t>
+          <t>0.070322586035337</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1794.372</t>
+          <t>0.0846669497123239</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1822.272</t>
+          <t>0.101727621941015</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1879.502</t>
+          <t>0.108573752616558</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1967.909</t>
+          <t>0.0913356413726129</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2028.019</t>
+          <t>0.101149408161629</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1998.675</t>
+          <t>0.0570984739319639</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1994.464</t>
+          <t>0.0665538130768046</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2034.281</t>
+          <t>0.0727406127628902</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2073.41</t>
+          <t>0.0738392025816077</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2103.397</t>
+          <t>0.0663927281191349</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2128.955</t>
+          <t>0.0588798694300013</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>72915.5501116402</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>75586.0398794097</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>89641.5211579208</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>102854.018838523</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>113942.755610106</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>126651.961675891</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>139105.301433405</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>169560.483458525</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>196014.3627115</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>179520.170709978</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>191247.804084582</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>219225.33161615</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>225328.677503809</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>236163.18151627</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>230440.226408123</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2741.309</t>
+          <t>78028.3749192772</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2859.475</t>
+          <t>80985.9328967418</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>3000.298</t>
+          <t>95922.756360814</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>3066.857</t>
+          <t>110170.981708347</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>3298.455</t>
+          <t>122025.243507881</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3304.827</t>
+          <t>135312.393482932</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>3450.037</t>
+          <t>148591.566544745</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>3610.65</t>
+          <t>180305.322098969</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3688.957</t>
+          <t>207195.93247822</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3548.203</t>
+          <t>190419.32413751</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>3223.105</t>
+          <t>202069.863592381</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>3616.979</t>
+          <t>231570.19161041</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>3360.782</t>
+          <t>237890.404897611</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>3735.256</t>
+          <t>249440.376640236</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>3762.522</t>
+          <t>243143.963322222</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>436115.207490924</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>450358.784317831</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>522856.905898737</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>599820.983801101</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>679159.523636757</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>768291.74424481</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>844000.213257616</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>1029605.06014961</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>1179640.13277467</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>1110706.35252739</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>1201226.02613738</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>1384901.39606438</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>1413383.49397177</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>1479257.9756484</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>1471086.95179907</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>122169.822456739</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.123</t>
+          <t>126365.9068654</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>133602.841229854</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.906</t>
+          <t>131287.15287377</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>132332.015923228</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>129312.944044329</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>134355.562201427</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>134950.280454151</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>139960.688609969</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>140856.811592655</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>138933.554819263</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>143017.456271887</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>148007.130278909</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>151825.356478706</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>154602.515505014</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>115412.221507146</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>119266.135750643</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>123941.154294431</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>121226.811178632</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>122888.543747242</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>120616.218596994</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>125533.508735255</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>126789.385929236</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>132203.308307374</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>132729.424595369</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>131492.828793296</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>135281.507172334</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>139835.535759226</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>143511.704127461</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>146392.751675172</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>73370.6090591112</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>72761.9246432582</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>77616.496562122</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>91643.2478771143</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>112936.413475699</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>140221.873320934</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>159879.900156292</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>176358.818685031</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>214314.36644978</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>156286.38179749</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>179962.269966975</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>214309.62805759</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>219067.535926389</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>218906.900675945</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>205988.47717978</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3.045e+09</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3.005e+09</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2.987e+09</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2.926e+09</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2.99e+09</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>3.049e+09</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>3.152e+09</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>3.323e+09</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3.456e+09</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3.389e+09</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>3.399e+09</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3.467e+09</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>3.531e+09</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>3.562e+09</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>3.614e+09</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3293210040.65503</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3249444885.27786</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>3223563931.32518</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>3165899302.06539</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>3229614804.47456</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>3280768157.51993</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>3384942137.96087</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>3549279257.00595</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>3672623155.76729</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3618798931.27386</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>3612940317.49222</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>3685377759.04541</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>3751592854.95187</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>3785210097.90135</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>3830627170.65573</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1811708660.88038</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1784686562.74579</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1784168646.7396</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1764478461.78814</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1794371980.33151</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1822272365.42764</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1879502211.08376</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1967908994.21834</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2028019102.78388</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1998674666.50442</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1994463505.61309</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2034281220.6357</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2073409714.54964</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2103396570.77324</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2128954509.95639</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2328000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2330000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2343000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2318000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2331000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2362000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2442000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2542000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2626000</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2612000</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2601000</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2638000</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2689000</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2727000</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2747000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2155000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2159000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2171000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2144000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2156000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2193000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2270000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2374000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2464000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2443000</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2442000</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2476000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2526000</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2562000</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2588000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3293210040.65503</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3249444885.27786</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3223563931.32518</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3165899302.06539</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3229614804.47456</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3280768157.51993</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3384942137.96087</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>3549279257.00595</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>3672623155.76729</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3618798931.27386</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>3612940317.49222</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>3685377759.04541</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>3751592854.95187</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>3785210097.90135</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>3830627170.65573</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3.045e+09</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3.005e+09</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2.987e+09</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2.926e+09</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2.99e+09</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3.049e+09</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3.152e+09</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3.323e+09</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3.456e+09</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3.389e+09</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>3.399e+09</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>3.467e+09</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>3.531e+09</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>3.562e+09</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>3.614e+09</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>277219.052132</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>283967.45162</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>322105.353592</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>371147.840972</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>427152.010912</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>495268.35504</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>559533.699036</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>668111.836196</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>779494.002248</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>646524.762065</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>700849.568606</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>815806.182</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>832712.786136</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>858418.687865</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>835078.908764</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>151398.756208</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>153747.9688</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>173539.126849</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>201814.088954</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>234961.359904</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>275533.95624</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>308471.77881</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>356664.311842</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>421510.298928</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>346705.705935</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>382032.299191</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>445879.819668</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>456957.940824</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>468347.447642</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>449132.121946</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>645293.601595254</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>666819.228126666</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>683279.112393686</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>673612.673530537</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>684205.847749086</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>691311.584113677</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>709383.478048119</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>768727.172676689</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>768619.88900034</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>830538.085057171</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>825905.510198592</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>839735.63395038</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>868921.796301258</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>893146.909582215</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>937498.933330622</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
